--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -319,6 +319,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1077,12 +1126,6 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25"/>
     <row r="36" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>23</v>
@@ -1620,5 +1663,6 @@
     <mergeCell ref="A69:K69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -290,10 +290,149 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="20">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -302,8 +441,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,7 +876,7 @@
       <c r="B7"/>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8"/>
@@ -728,7 +886,7 @@
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J8"/>
@@ -740,7 +898,7 @@
       <c r="P8"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9"/>
@@ -750,7 +908,7 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9"/>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J9"/>
@@ -834,7 +992,7 @@
       <c r="P13"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B14"/>
@@ -844,7 +1002,7 @@
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J14"/>
@@ -856,7 +1014,7 @@
       <c r="P14"/>
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B15"/>
@@ -866,6 +1024,7 @@
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
+      <c r="I15" s="3"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
@@ -874,7 +1033,7 @@
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
@@ -883,11 +1042,14 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16"/>
-      <c r="I16" t="s">
+      <c r="I16" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -899,8 +1061,9 @@
       <c r="I17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -909,11 +1072,12 @@
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18"/>
-      <c r="I18" t="s">
+      <c r="I18" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P18" s="7"/>
+    </row>
+    <row r="19" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -922,11 +1086,12 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19"/>
-      <c r="I19" t="s">
+      <c r="I19" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -935,6 +1100,8 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20"/>
+      <c r="I20" s="4"/>
+      <c r="P20" s="6"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21"/>
@@ -945,7 +1112,7 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J21"/>
@@ -993,14 +1160,19 @@
       <c r="P23"/>
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B24"/>
-      <c r="C24" t="s">
+      <c r="C24" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I24" t="s">
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="10" t="s">
         <v>15</v>
       </c>
       <c r="J24"/>
@@ -1008,17 +1180,17 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" t="s">
+      <c r="O24" s="11" t="s">
         <v>16</v>
       </c>
       <c r="P24"/>
     </row>
     <row r="25" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B25"/>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D25"/>
@@ -1026,22 +1198,23 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25"/>
+      <c r="I25" s="9"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
       <c r="M25"/>
       <c r="N25"/>
-      <c r="O25" t="s">
+      <c r="O25" s="12" t="s">
         <v>19</v>
       </c>
       <c r="P25"/>
     </row>
     <row r="26" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B26"/>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26"/>
@@ -1049,7 +1222,7 @@
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26"/>
-      <c r="I26" t="s">
+      <c r="I26" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J26"/>
@@ -1079,11 +1252,11 @@
       <c r="P27"/>
     </row>
     <row r="28" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B28"/>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D28"/>
@@ -1091,7 +1264,7 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28"/>
-      <c r="I28" t="s">
+      <c r="I28" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J28"/>
@@ -1103,11 +1276,11 @@
       <c r="P28"/>
     </row>
     <row r="29" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B29"/>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D29"/>
@@ -1117,7 +1290,7 @@
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
-      <c r="K29" t="s">
+      <c r="K29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L29"/>
@@ -1126,14 +1299,83 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="4"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="4"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="4"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="4"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="4"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="4"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="4"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="4"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="7"/>
+    </row>
+    <row r="36" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D36" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E36"/>
@@ -1142,20 +1384,27 @@
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36"/>
-      <c r="K36" t="s">
+      <c r="K36" s="17" t="s">
         <v>26</v>
       </c>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="18"/>
     </row>
     <row r="37" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="19"/>
       <c r="B37"/>
       <c r="C37"/>
+      <c r="D37" s="19"/>
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37"/>
-      <c r="K37" t="s">
+      <c r="K37" s="19" t="s">
         <v>27</v>
       </c>
       <c r="L37"/>
@@ -1165,14 +1414,17 @@
       <c r="P37"/>
     </row>
     <row r="38" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
       <c r="B38"/>
       <c r="C38"/>
+      <c r="D38" s="3"/>
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38"/>
+      <c r="K38" s="3"/>
       <c r="L38"/>
       <c r="M38"/>
       <c r="N38"/>
@@ -1180,7 +1432,7 @@
       <c r="P38"/>
     </row>
     <row r="39" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B39"/>
@@ -1199,22 +1451,32 @@
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
         <v>29</v>
       </c>
+      <c r="B40" s="8"/>
       <c r="C40"/>
-      <c r="D40" t="s">
+      <c r="D40" s="9" t="s">
         <v>30</v>
       </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
       <c r="H40"/>
       <c r="I40"/>
-      <c r="K40" t="s">
+      <c r="J40" s="8"/>
+      <c r="K40" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="8"/>
     </row>
     <row r="41" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B41"/>
@@ -1252,14 +1514,14 @@
       <c r="P42"/>
     </row>
     <row r="43" ht="10.15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G43"/>
@@ -1273,19 +1535,19 @@
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" ht="10.9" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" ht="10.9" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B44"/>
-      <c r="C44" t="s">
+      <c r="C44" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E44"/>
-      <c r="F44" t="s">
+      <c r="F44" s="13" t="s">
         <v>38</v>
       </c>
       <c r="H44" t="s">
@@ -1303,12 +1565,15 @@
       <c r="O44" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="P44" s="6"/>
+    </row>
+    <row r="45" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B45"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="1"/>
       <c r="E45"/>
       <c r="F45" t="s">
         <v>38</v>
@@ -1328,8 +1593,9 @@
       <c r="O45" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P45" s="6"/>
+    </row>
+    <row r="46" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
@@ -1353,12 +1619,15 @@
       <c r="O46" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="P46" s="6"/>
+    </row>
+    <row r="47" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B47"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="1"/>
       <c r="E47"/>
       <c r="F47" t="s">
         <v>38</v>
@@ -1378,8 +1647,9 @@
       <c r="O47" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="48" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47" s="6"/>
+    </row>
+    <row r="48" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
@@ -1403,8 +1673,12 @@
       <c r="O48" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="49" ht="10" customHeight="1" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="P48" s="6"/>
+    </row>
+    <row r="49" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="1"/>
       <c r="E49"/>
       <c r="F49" t="s">
         <v>38</v>
@@ -1424,31 +1698,56 @@
       <c r="O49" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="50" ht="10" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P49" s="6"/>
+    </row>
+    <row r="50" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
       <c r="B50"/>
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
-      <c r="F50" t="s">
+      <c r="F50" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H50" t="s">
+      <c r="G50" s="16"/>
+      <c r="H50" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="7"/>
+    </row>
+    <row r="51" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="L51" t="s">
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="10" t="s">
         <v>56</v>
       </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="14"/>
     </row>
     <row r="52" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="19"/>
       <c r="B52"/>
       <c r="C52"/>
       <c r="D52"/>
@@ -1459,15 +1758,17 @@
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
+      <c r="L52" s="19"/>
       <c r="M52"/>
       <c r="N52"/>
       <c r="O52"/>
       <c r="P52"/>
     </row>
     <row r="53" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="15" t="s">
         <v>57</v>
       </c>
+      <c r="B53" s="7"/>
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
@@ -1477,7 +1778,7 @@
       <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
-      <c r="L53" t="s">
+      <c r="L53" s="3" t="s">
         <v>58</v>
       </c>
       <c r="M53"/>
@@ -1485,108 +1786,150 @@
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="54" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="55" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="14"/>
+    </row>
+    <row r="55" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="56" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="P55" s="6"/>
+    </row>
+    <row r="56" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="57" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="P56" s="6"/>
+    </row>
+    <row r="57" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B57" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="58" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="P57" s="6"/>
+    </row>
+    <row r="58" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="59" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="P58" s="6"/>
+    </row>
+    <row r="59" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B59" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="60" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="P59" s="6"/>
+    </row>
+    <row r="60" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="61" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="P60" s="6"/>
+    </row>
+    <row r="61" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B61" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="62" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="P61" s="6"/>
+    </row>
+    <row r="62" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B62" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="63" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="P62" s="6"/>
+    </row>
+    <row r="63" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B63" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="64" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="P63" s="6"/>
+    </row>
+    <row r="64" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B64" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="65" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="P64" s="6"/>
+    </row>
+    <row r="65" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B65" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="66" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="P65" s="6"/>
+    </row>
+    <row r="66" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B66" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="67" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="P66" s="6"/>
+    </row>
+    <row r="67" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
         <v>83</v>
       </c>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="7"/>
     </row>
     <row r="68" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -290,7 +290,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -303,112 +303,132 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="medium"/>
       <top style="medium"/>
       <bottom style="thin"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="medium"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="medium"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="medium"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
       <right/>
       <top/>
-      <bottom style="thin"/>
-      <diagonal/>
+      <bottom/>
     </border>
     <border>
       <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium"/>
       <right/>
       <top/>
-      <bottom style="thin"/>
-      <diagonal/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin"/>
@@ -417,7 +437,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -428,40 +447,44 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf borderId="1" applyBorder="1"/>
+    <xf borderId="2" applyBorder="1"/>
+    <xf borderId="3" applyBorder="1"/>
+    <xf borderId="4" applyBorder="1"/>
+    <xf borderId="5" applyBorder="1"/>
+    <xf borderId="6" applyBorder="1"/>
+    <xf borderId="7" applyBorder="1"/>
+    <xf borderId="8" applyBorder="1"/>
+    <xf borderId="9" applyBorder="1"/>
+    <xf borderId="10" applyBorder="1"/>
+    <xf borderId="11" applyBorder="1"/>
+    <xf borderId="12" applyBorder="1"/>
+    <xf borderId="13" applyBorder="1"/>
+    <xf borderId="14" applyBorder="1"/>
+    <xf borderId="15" applyBorder="1"/>
+    <xf borderId="16" applyBorder="1"/>
+    <xf borderId="17" applyBorder="1"/>
+    <xf borderId="18" applyBorder="1"/>
+    <xf borderId="19" applyBorder="1"/>
+    <xf borderId="20" applyBorder="1"/>
+    <xf borderId="21" applyBorder="1"/>
+    <xf borderId="22" applyBorder="1"/>
+    <xf borderId="23" applyBorder="1"/>
+    <xf borderId="24" applyBorder="1"/>
+    <xf borderId="25" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -879,675 +902,676 @@
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-      <c r="P8"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="3"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
       <c r="I9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10"/>
+      <c r="A10" s="7"/>
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="7"/>
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
       <c r="O10"/>
-      <c r="P10"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11"/>
+      <c r="A11" s="7"/>
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="7"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
-      <c r="P11"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12"/>
+      <c r="A12" s="7"/>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="7"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
-      <c r="P12"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13"/>
+      <c r="A13" s="7"/>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-      <c r="P13"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-      <c r="P14"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="3"/>
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I15" s="12"/>
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15" s="3"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="P16" s="8"/>
+      <c r="A16" s="7"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="8"/>
+      <c r="I16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P17" s="8"/>
+      <c r="A17" s="7"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17"/>
+      <c r="H17" s="8"/>
       <c r="I17" t="s">
         <v>9</v>
       </c>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18"/>
+    </row>
+    <row r="18" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P18" s="11"/>
+      <c r="A18" s="7"/>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19"/>
+    </row>
+    <row r="19" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="P19" s="3"/>
+      <c r="A19" s="7"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19" s="4" t="s">
+      <c r="H19" s="8"/>
+      <c r="I19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P19" s="8"/>
-    </row>
-    <row r="20" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20"/>
+    </row>
+    <row r="20" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="7"/>
+      <c r="P20" s="8"/>
+      <c r="A20" s="7"/>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20" s="4"/>
-      <c r="P20" s="6"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21"/>
+      <c r="A21" s="7"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
-      <c r="H21"/>
+      <c r="H21" s="8"/>
       <c r="I21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
-      <c r="P21"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22"/>
+      <c r="A22" s="7"/>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="7"/>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22"/>
-      <c r="P22"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="23" ht="13.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
       <c r="O23"/>
-      <c r="P23"/>
+      <c r="P23" s="8"/>
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="3"/>
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B24"/>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24" s="11" t="s">
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="P24"/>
+      <c r="P24" s="16"/>
     </row>
     <row r="25" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I25" s="13"/>
       <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B25"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25" s="9"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25" s="12" t="s">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="P25"/>
+      <c r="P25" s="18"/>
     </row>
     <row r="26" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B26"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26" s="9" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="20"/>
     </row>
     <row r="27" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="20"/>
     </row>
     <row r="28" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B28"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28" s="9" t="s">
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="22"/>
     </row>
     <row r="29" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B29"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
       <c r="K29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-      <c r="P29"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="8"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="4"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="4"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="4"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="4"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="4"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="4"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="4"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="4"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="7"/>
-    </row>
-    <row r="36" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="11"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="7"/>
+      <c r="P31" s="8"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="7"/>
+      <c r="P32" s="8"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="7"/>
+      <c r="P33" s="8"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="7"/>
+      <c r="P34" s="8"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="11"/>
+    </row>
+    <row r="36" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C36" s="2"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="24"/>
+      <c r="A36" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="5"/>
       <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36" s="17" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="18"/>
     </row>
     <row r="37" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="19"/>
+      <c r="A37" s="25"/>
+      <c r="D37" s="25"/>
       <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37" s="19"/>
+      <c r="C37" s="8"/>
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37" s="19" t="s">
+      <c r="J37" s="8"/>
+      <c r="K37" s="25" t="s">
         <v>27</v>
       </c>
       <c r="L37"/>
       <c r="M37"/>
       <c r="N37"/>
       <c r="O37"/>
-      <c r="P37"/>
+      <c r="P37" s="8"/>
     </row>
     <row r="38" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38"/>
-      <c r="C38"/>
-      <c r="D38" s="3"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-      <c r="K38" s="3"/>
-      <c r="L38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-      <c r="P38"/>
+      <c r="A38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="11"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="11"/>
     </row>
     <row r="39" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B39"/>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-      <c r="P39"/>
-    </row>
-    <row r="40" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="J40" s="3"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="3"/>
+      <c r="A40" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40"/>
-      <c r="D40" s="9" t="s">
+      <c r="C40" s="3"/>
+      <c r="D40" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="9" t="s">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="K40" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="8"/>
     </row>
     <row r="41" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B41"/>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
-      <c r="P41"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="6"/>
     </row>
     <row r="42" ht="13.9" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="11"/>
     </row>
     <row r="43" ht="10.15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="3"/>
       <c r="F43" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
-      <c r="P43"/>
-    </row>
-    <row r="44" ht="10.9" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" ht="10.9" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44" s="8"/>
       <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B44"/>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="3"/>
+      <c r="C44" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E44"/>
-      <c r="F44" s="13" t="s">
+      <c r="E44" s="3"/>
+      <c r="F44" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H44" t="s">
@@ -1565,16 +1589,16 @@
       <c r="O44" t="s">
         <v>41</v>
       </c>
-      <c r="P44" s="6"/>
-    </row>
-    <row r="45" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C45" s="13"/>
+      <c r="D45" s="1"/>
+      <c r="P45" s="8"/>
       <c r="A45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B45"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="1"/>
-      <c r="E45"/>
+      <c r="B45" s="6"/>
+      <c r="E45" s="6"/>
       <c r="F45" t="s">
         <v>38</v>
       </c>
@@ -1593,14 +1617,14 @@
       <c r="O45" t="s">
         <v>44</v>
       </c>
-      <c r="P45" s="6"/>
-    </row>
-    <row r="46" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
+    </row>
+    <row r="46" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46" s="8"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="11"/>
       <c r="F46" t="s">
         <v>38</v>
       </c>
@@ -1619,16 +1643,16 @@
       <c r="O46" t="s">
         <v>46</v>
       </c>
-      <c r="P46" s="6"/>
-    </row>
-    <row r="47" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C47" s="13"/>
+      <c r="D47" s="1"/>
+      <c r="P47" s="8"/>
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B47"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="1"/>
-      <c r="E47"/>
+      <c r="B47" s="6"/>
+      <c r="E47" s="6"/>
       <c r="F47" t="s">
         <v>38</v>
       </c>
@@ -1647,14 +1671,14 @@
       <c r="O47" t="s">
         <v>49</v>
       </c>
-      <c r="P47" s="6"/>
-    </row>
-    <row r="48" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-      <c r="C48"/>
-      <c r="D48"/>
-      <c r="E48"/>
+    </row>
+    <row r="48" ht="10" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P48" s="8"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="11"/>
       <c r="F48" t="s">
         <v>38</v>
       </c>
@@ -1673,13 +1697,13 @@
       <c r="O48" t="s">
         <v>51</v>
       </c>
-      <c r="P48" s="6"/>
-    </row>
-    <row r="49" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="C49" s="9"/>
+    </row>
+    <row r="49" ht="10" customHeight="1" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="7"/>
+      <c r="C49" s="13"/>
       <c r="D49" s="1"/>
-      <c r="E49"/>
+      <c r="P49" s="8"/>
+      <c r="E49" s="6"/>
       <c r="F49" t="s">
         <v>38</v>
       </c>
@@ -1698,56 +1722,56 @@
       <c r="O49" t="s">
         <v>53</v>
       </c>
-      <c r="P49" s="6"/>
-    </row>
-    <row r="50" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50" s="16" t="s">
+    </row>
+    <row r="50" ht="10" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+      <c r="G50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16" t="s">
+      <c r="H50" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I50" s="16" t="s">
+      <c r="I50" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16"/>
-      <c r="P50" s="7"/>
-    </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+    </row>
+    <row r="51" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="6"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="6"/>
+      <c r="A51" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="10" t="s">
+      <c r="L51" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="14"/>
     </row>
     <row r="52" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="19"/>
+      <c r="A52" s="25"/>
+      <c r="L52" s="25"/>
       <c r="B52"/>
       <c r="C52"/>
       <c r="D52"/>
@@ -1757,179 +1781,178 @@
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52" s="19"/>
+      <c r="K52" s="8"/>
       <c r="M52"/>
       <c r="N52"/>
       <c r="O52"/>
-      <c r="P52"/>
+      <c r="P52" s="8"/>
     </row>
     <row r="53" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+      <c r="B53" s="11"/>
+      <c r="A53" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53" s="3" t="s">
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
-      <c r="P53"/>
-    </row>
-    <row r="54" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="11"/>
+    </row>
+    <row r="54" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="6"/>
+      <c r="A54" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="14"/>
-    </row>
-    <row r="55" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+    </row>
+    <row r="55" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P55" s="8"/>
+      <c r="A55" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
       </c>
-      <c r="P55" s="6"/>
-    </row>
-    <row r="56" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
+    </row>
+    <row r="56" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P56" s="8"/>
+      <c r="A56" s="7" t="s">
         <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
       </c>
-      <c r="P56" s="6"/>
-    </row>
-    <row r="57" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+    </row>
+    <row r="57" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P57" s="8"/>
+      <c r="A57" s="7" t="s">
         <v>64</v>
       </c>
       <c r="B57" t="s">
         <v>65</v>
       </c>
-      <c r="P57" s="6"/>
-    </row>
-    <row r="58" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+    </row>
+    <row r="58" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P58" s="8"/>
+      <c r="A58" s="7" t="s">
         <v>66</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
-      <c r="P58" s="6"/>
-    </row>
-    <row r="59" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+    </row>
+    <row r="59" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P59" s="8"/>
+      <c r="A59" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B59" t="s">
         <v>69</v>
       </c>
-      <c r="P59" s="6"/>
-    </row>
-    <row r="60" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
+    </row>
+    <row r="60" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="P60" s="8"/>
+      <c r="A60" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="P60" s="6"/>
-    </row>
-    <row r="61" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
+    </row>
+    <row r="61" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P61" s="8"/>
+      <c r="A61" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B61" t="s">
         <v>72</v>
       </c>
-      <c r="P61" s="6"/>
-    </row>
-    <row r="62" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+    </row>
+    <row r="62" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P62" s="8"/>
+      <c r="A62" s="7" t="s">
         <v>73</v>
       </c>
       <c r="B62" t="s">
         <v>74</v>
       </c>
-      <c r="P62" s="6"/>
-    </row>
-    <row r="63" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
+    </row>
+    <row r="63" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P63" s="8"/>
+      <c r="A63" s="7" t="s">
         <v>75</v>
       </c>
       <c r="B63" t="s">
         <v>76</v>
       </c>
-      <c r="P63" s="6"/>
-    </row>
-    <row r="64" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+    </row>
+    <row r="64" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P64" s="8"/>
+      <c r="A64" s="7" t="s">
         <v>77</v>
       </c>
       <c r="B64" t="s">
         <v>78</v>
       </c>
-      <c r="P64" s="6"/>
-    </row>
-    <row r="65" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+    </row>
+    <row r="65" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P65" s="8"/>
+      <c r="A65" s="7" t="s">
         <v>79</v>
       </c>
       <c r="B65" t="s">
         <v>80</v>
       </c>
-      <c r="P65" s="6"/>
-    </row>
-    <row r="66" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+    </row>
+    <row r="66" ht="10" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="P66" s="8"/>
+      <c r="A66" s="7" t="s">
         <v>81</v>
       </c>
       <c r="B66" t="s">
         <v>82</v>
       </c>
-      <c r="P66" s="6"/>
-    </row>
-    <row r="67" ht="10" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
+    </row>
+    <row r="67" ht="10" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="11"/>
+      <c r="A67" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="16"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="16"/>
-      <c r="O67" s="16"/>
-      <c r="P67" s="7"/>
     </row>
     <row r="68" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf borderId="1" applyBorder="1"/>
     <xf borderId="2" applyBorder="1"/>
@@ -485,6 +485,12 @@
     <xf borderId="23" applyBorder="1"/>
     <xf borderId="24" applyBorder="1"/>
     <xf borderId="25" applyBorder="1"/>
+    <xf applyAlignment="1" borderId="4" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="1" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -921,8 +927,10 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>4</v>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.address}}</t>
+        </is>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1038,8 +1046,10 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I15" s="12"/>
-      <c r="A15" s="1" t="s">
-        <v>7</v>
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.address}}</t>
+        </is>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>

--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf borderId="1" applyBorder="1"/>
     <xf borderId="2" applyBorder="1"/>
@@ -491,6 +491,12 @@
     <xf applyAlignment="1" borderId="1" applyBorder="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf applyAlignment="1" borderId="4" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="1" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,19 +516,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="6086973" cy="1271905"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -553,7 +554,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -927,7 +928,7 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">{{shipper.address}}</t>
         </is>
@@ -1046,7 +1047,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="I15" s="12"/>
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">{{consignee.address}}</t>
         </is>
